--- a/train.xlsx
+++ b/train.xlsx
@@ -13,9 +13,9 @@
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="26.1.27 version（102个）" sheetId="2" r:id="rId1"/>
-    <sheet name="25.12.3 version（110个）" sheetId="3" r:id="rId2"/>
-    <sheet name="25.10.10 version（120）" sheetId="4" r:id="rId3"/>
+    <sheet name="26.1.27 version(102 items)" sheetId="2" r:id="rId1"/>
+    <sheet name="25.12.3 version(110 items)" sheetId="3" r:id="rId2"/>
+    <sheet name="25.10.10 version(120)" sheetId="4" r:id="rId3"/>
     <sheet name="25.8.7 version" sheetId="5" r:id="rId4"/>
     <sheet name="25.7.20 version" sheetId="6" r:id="rId5"/>
     <sheet name="25.7.19 version" sheetId="7" r:id="rId6"/>
@@ -41,26 +41,26 @@
   <commentList>
     <comment ref="H31" authorId="0" shapeId="0" xr:uid="{13F3242D-3C96-4BAF-8E56-D37E0E60D55A}">
       <text>
-        <t>[线程批注]
-你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
-注释:
-    本身部分展开就是SOS？</t>
+        <t>[Threaded comment]
+Your Excel version can read this threaded comment; if the file is opened in a newer Excel version, any changes made to the comment will be deleted. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Is the partial expansion itself SOS?</t>
       </text>
     </comment>
     <comment ref="C41" authorId="1" shapeId="0" xr:uid="{6A84E58D-0B2C-4B23-B644-E10E2FB2A9FB}">
       <text>
-        <t>[线程批注]
-你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
-注释:
-    由于r=1时，二次舒尔不等式经过平方换元后和Robinson不等式重复了，所以这里换成四次舒尔不等式再平方换元</t>
+        <t>[Threaded comment]
+Your Excel version can read this threaded comment; if the file is opened in a newer Excel version, any changes made to the comment will be deleted. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    When r=1, the quadratic Schur inequality duplicates the Robinson inequality after square substitution, so this is changed to the quartic Schur inequality followed by square substitution</t>
       </text>
     </comment>
     <comment ref="H45" authorId="2" shapeId="0" xr:uid="{B1015C5D-D2D7-4328-8F98-E690265FCF2E}">
       <text>
-        <t>[线程批注]
-你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
-注释:
-    为了方便找SOS，可能还是展开比较好?</t>
+        <t>[Threaded comment]
+Your Excel version can read this threaded comment; if the file is opened in a newer Excel version, any changes made to the comment will be deleted. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    For easier SOS search, expansion may still be better?</t>
       </text>
     </comment>
   </commentList>
@@ -70,40 +70,40 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5420" uniqueCount="507">
   <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>来源</t>
-  </si>
-  <si>
-    <t>题号</t>
-  </si>
-  <si>
-    <t>初始来源</t>
-  </si>
-  <si>
-    <t>原作者</t>
-  </si>
-  <si>
-    <t>类别</t>
-  </si>
-  <si>
-    <t>是否需要转化</t>
-  </si>
-  <si>
-    <t>sympy格式</t>
+    <t>SampleID</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>ProblemNumber</t>
+  </si>
+  <si>
+    <t>InitialSource</t>
+  </si>
+  <si>
+    <t>OriginalAuthor</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>NeedsTransformation</t>
+  </si>
+  <si>
+    <t>SympyFormat</t>
   </si>
   <si>
     <t>latex</t>
   </si>
   <si>
-    <t>变元数量</t>
-  </si>
-  <si>
-    <t xml:space="preserve">多项式次数 </t>
-  </si>
-  <si>
-    <t>？难度级别</t>
+    <t>number of variables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PolynomialDegree </t>
+  </si>
+  <si>
+    <t>?difficulty level</t>
   </si>
   <si>
     <t xml:space="preserve">Evan_chen.lean </t>
@@ -118,10 +118,10 @@
     <t>Evan Chen</t>
   </si>
   <si>
-    <t>竞赛级别</t>
-  </si>
-  <si>
-    <t>否</t>
+    <t>contest level</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
   <si>
     <t>x1**2 - x1*x2 - x1*x3 + x2**2 - x2*x3 + x3**2</t>
@@ -154,16 +154,16 @@
     <t>567 Nice And Hard Inequalities</t>
   </si>
   <si>
-    <t>无（仅移项）</t>
+    <t>None(only moved terms)</t>
   </si>
   <si>
     <t>-2*x1**4 + 2*x1**2*x2**2 + 2*x1**2*x3**2 + x2**4 - 4*x2**2*x3**2 + x3**4</t>
   </si>
   <si>
-    <t>Olympiad Inequalities 數學奧林匹克的不等式</t>
-  </si>
-  <si>
-    <t>练习题3</t>
+    <t>Olympiad Inequalities Mathematical Olympiad inequalities</t>
+  </si>
+  <si>
+    <t>Exercise 3</t>
   </si>
   <si>
     <t>x1**3 - x1**2*x2 + x2**3 - x2**2*x3 + x3**3 - x1*x3**2</t>
@@ -190,7 +190,7 @@
     <t xml:space="preserve"> P84</t>
   </si>
   <si>
-    <t>平方换元</t>
+    <t>square substitution</t>
   </si>
   <si>
     <t>5*x1**4 - x1**2*x2**2 - 8*x1**2*x3**2 - x1**2*x4**2 + 5*x2**4 - x2**2*x3**2 - 8*x2**2*x4**2 + 5*x3**4 - x3**2*x4**2 + 5*x4**4</t>
@@ -199,10 +199,10 @@
     <t>[2015] An algorithm for decomposing a non-negative polynomial as a sum of squares of rational functions</t>
   </si>
   <si>
-    <t>Peyri-Parrilo 多项式</t>
-  </si>
-  <si>
-    <t>有名例子</t>
+    <t>Peyri-Parrilo Polynomial</t>
+  </si>
+  <si>
+    <t>famous example</t>
   </si>
   <si>
     <t>(2 * x4**2 - 2 * x3 * x4 + 8 * x3**2 - 2 * x2 * x3 + x2**2 
@@ -229,7 +229,7 @@
     <t>[2012] Exact certification in global polynomial optimization via sums-of-squares of rational functions with rational coefficients</t>
   </si>
   <si>
-    <t>Lax-Lax 多项式</t>
+    <t>Lax-Lax Polynomial</t>
   </si>
   <si>
     <t>(x1 * x2 * x3 * x4 
@@ -242,7 +242,7 @@
     <t>[2023] SUM OF SQUARES DECOMPOSITIONS OF POLYNOMIALS OVER THEIR GRADIENT IDEALS WITH RATIONAL COEFFICIENTS</t>
   </si>
   <si>
-    <t xml:space="preserve">  Example 3.6 Scheiderer引入</t>
+    <t xml:space="preserve">  Example 3.6 introduced by Scheiderer</t>
   </si>
   <si>
     <t>(
@@ -251,13 +251,13 @@
 )</t>
   </si>
   <si>
-    <t>118个数学竞赛不等式</t>
-  </si>
-  <si>
-    <t>例36</t>
-  </si>
-  <si>
-    <t>简单通分，平方换元</t>
+    <t>118 Math contest inequalities</t>
+  </si>
+  <si>
+    <t>Example 36</t>
+  </si>
+  <si>
+    <t>simple common-denominator conversion,square substitution</t>
   </si>
   <si>
     <t>48*x1**4*x3**4 + 36*x1**4 - 16*x1**2 + 24*x2**4*x3**4 + 18*x2**4 - 16*x2**2 + 12*x3**4 - 16*x3**2 + 9</t>
@@ -323,7 +323,7 @@
     <t>x1**6 + x2**6 + x3**6 - 3*x1**2*x2**2*x3**2</t>
   </si>
   <si>
-    <t>Robinson 多项式</t>
+    <t>Robinson Polynomial</t>
   </si>
   <si>
     <t>(x3**6 - x2**4 * x3**2 - x2**2 * x3**4 + x2**6 - x1**2 * x3**4 
@@ -337,10 +337,10 @@
     <t>IMO 1964 Q2</t>
   </si>
   <si>
-    <t>IMO级别</t>
-  </si>
-  <si>
-    <t>三角形约束转化</t>
+    <t>IMO level</t>
+  </si>
+  <si>
+    <t>triangle-constraint transformation</t>
   </si>
   <si>
     <t xml:space="preserve">x1**6 + x2**6 + x3**6 + 3*x1**2*x2**2*x3**2 - x1**2*x2**2*(x2**2+x3**2) - x2**2*x3**2*(x2**2+x3**2) - x3**2*x1**2*(x3**2 + x1**2) </t>
@@ -352,7 +352,7 @@
     <t>Q13</t>
   </si>
   <si>
-    <t>有名例子？</t>
+    <t>famous example?</t>
   </si>
   <si>
     <t>x1**6 + x1**2*x2**2*x3**2 - 4*x1**2 + x2**6 - 4*x2**2 + x3**6 - 4*x3**2 + 8</t>
@@ -460,7 +460,7 @@
     <t>Mircea Lascu (Mircea Lascu)</t>
   </si>
   <si>
-    <t>平方换元 简单通分</t>
+    <t>square substitution simple common-denominator conversion</t>
   </si>
   <si>
     <t>x1**4*x3**2 + x1**2*x2**4 - x1**2*x2**2*x3**2 - 2*x1**2*x3**4 + x2**2*x3**4 + x3**6</t>
@@ -475,22 +475,22 @@
     <t>Czech-Slovak Match 1999</t>
   </si>
   <si>
-    <t>平方换元 通分</t>
+    <t>square substitution common-denominator conversion</t>
   </si>
   <si>
     <t>2*x1**6 + 2*x1**4*x2**2 - 3*x1**4*x3**2 - 3*x1**2*x2**4 - 3*x1**2*x2**2*x3**2 + 2*x1**2*x3**4 + 2*x2**6 + 2*x2**4*x3**2 - 3*x2**2*x3**4 + 2*x3**6</t>
   </si>
   <si>
-    <t>不等式问题集及答案</t>
+    <t>Inequality problem set and answers</t>
   </si>
   <si>
     <t>x1**4*x2**2 - x1**3*x2*x3**2 - x1**2*x2**3*x3 + x1**2*x3**4 - x1*x2**2*x3**3 + x2**4*x3**2</t>
   </si>
   <si>
-    <t>新增</t>
-  </si>
-  <si>
-    <t>1.3 练习题1</t>
+    <t>added</t>
+  </si>
+  <si>
+    <t>1.3 Exercise 1</t>
   </si>
   <si>
     <t>x1**7 - x1**4*x2**3 + x2**7 - x2**4*x3**3 + x3**7 - x1**3*x3**4</t>
@@ -499,7 +499,7 @@
     <t>None</t>
   </si>
   <si>
-    <t>（四次schur不等式）</t>
+    <t>(quartic Schur inequality)</t>
   </si>
   <si>
     <t>Schur‘s Inequality r=2</t>
@@ -508,7 +508,7 @@
     <t>x1**8 - x1**6*x2**2 - x1**6*x3**2 + x1**4*x2**2*x3**2 - x1**2*x2**6 + x1**2*x2**4*x3**2 + x1**2*x2**2*x3**4 - x1**2*x3**6 + x2**8 - x2**6*x3**2 - x2**2*x3**6 + x3**8</t>
   </si>
   <si>
-    <t>Delzell 多项式</t>
+    <t>Delzell Polynomial</t>
   </si>
   <si>
     <t>(x1**4 * x2**2 * x4**2 + x2**4 * x3**2 * x4**2 + x1**2 * x3**4 * x4**2 
@@ -524,7 +524,7 @@
     <t>x1**8 + 4*x1**6*x2**2 - 4*x1**6*x3**2 + 2*x1**4*x2**4 + 2*x1**4*x3**4 - 4*x1**2*x2**6 + 4*x1**2*x3**6 + x2**8 + 4*x2**6*x3**2 + 2*x2**4*x3**4 - 4*x2**2*x3**6 + x3**8</t>
   </si>
   <si>
-    <t>例26</t>
+    <t>Example 26</t>
   </si>
   <si>
     <t>x1**8 - x1**4*x2**2*x3**2 - x1**4*x2**2*x4**2 - x1**4*x3**2*x4**2 - x1**2*x2**4*x3**2 - x1**2*x2**4*x4**2 - x1**2*x2**2*x3**4 + 8*x1**2*x2**2*x3**2*x4**2 - x1**2*x2**2*x4**4 - x1**2*x3**4*x4**2 - x1**2*x3**2*x4**4 + x2**8 - x2**4*x3**2*x4**2 - x2**2*x3**4*x4**2 - x2**2*x3**2*x4**4 + x3**8 + x4**8</t>
@@ -536,7 +536,7 @@
     <t>x1**8 - 4*x1**2*x2**2*x3**2*x4**2 + x2**8 + x3**8 + x4**8 + (-x1**2 + x4**2)*(2*x1**2 - 2*x2**2)*(x2**2 - x3**2)*(x3**2 - x4**2)</t>
   </si>
   <si>
-    <t>为了方便找SOS，展开比较好？</t>
+    <t>For easier SOS search, expansion may be better?</t>
   </si>
   <si>
     <t>Q49</t>
@@ -563,7 +563,7 @@
     <t>Q 107</t>
   </si>
   <si>
-    <t>平方换元，简单通分</t>
+    <t>square substitution,simple common-denominator conversion</t>
   </si>
   <si>
     <t xml:space="preserve"> 12*x1**2*x2**2*x3**2*x4**2 - 3*x1**2*x2**2*x3**2 - 3*x1**2*x2**2*x4**2 - 3*x1**2*x3**2*x4**2 - 3*x2**2*x3**2*x4**2 + (x1**2*x2**2 + x1**2*x3**2 + x1**2*x4**2 + x2**2*x3**2 + x2**2*x4**2 + x3**2*x4**2)**2</t>
@@ -617,7 +617,7 @@
     <t>x1**6*x3**2 + x1**6*x4**2 + x1**4*x2**4 - x1**4*x2**2*x4**2 - 2*x1**4*x3**4 - x1**4*x3**2*x4**2 + x1**4*x4**4 + x1**2*x2**6 - x1**2*x2**4*x3**2 - x1**2*x2**4*x4**2 - x1**2*x2**2*x3**4 + x1**2*x3**6 - x1**2*x3**2*x4**4 + x2**6*x4**2 + x2**4*x3**4 - 2*x2**4*x4**4 + x2**2*x3**6 - x2**2*x3**4*x4**2 - x2**2*x3**2*x4**4 + x2**2*x4**6 + x3**4*x4**4 + x3**2*x4**6</t>
   </si>
   <si>
-    <t>新增有名例子</t>
+    <t>addedfamous example</t>
   </si>
   <si>
     <t>I 32</t>
@@ -686,7 +686,7 @@
     <t>[2008] Computing the Global Optimum of aMultiv ariate Polynomial over the Reals</t>
   </si>
   <si>
-    <t>vor1   Voronoi 多项式</t>
+    <t>vor1   Voronoi Polynomial</t>
   </si>
   <si>
     <t>(  
@@ -757,13 +757,13 @@
     <t>problem 40</t>
   </si>
   <si>
-    <t>Vasile Cartoaje （keyree10）</t>
+    <t>Vasile Cartoaje (keyree10)</t>
   </si>
   <si>
     <t>-81*x1**2*x2**2*x3**2*(x1**4 + x2**4 + x3**4) + (x1**2 + x2**2 + x3**2)**5</t>
   </si>
   <si>
-    <t>例90</t>
+    <t>Example 90</t>
   </si>
   <si>
     <t>AoPS</t>
@@ -811,7 +811,7 @@
     <t>x1**8*x2**2*x3**2 + x1**6*x2**6 + x1**6*x3**6 - 6*x1**4*x2**4*x3**4 + x1**2*x2**8*x3**2 + x1**2*x2**2*x3**8 + x2**6*x3**6</t>
   </si>
   <si>
-    <t xml:space="preserve"> 例5</t>
+    <t xml:space="preserve"> Example 5</t>
   </si>
   <si>
     <t>x1**8*x2**2*x3**2 + x1**6*x2**6 - x1**6*x2**4*x3**2 - x1**6*x2**2*x3**4 + x1**6*x3**6 - x1**4*x2**6*x3**2 - x1**4*x2**2*x3**6 + x1**2*x2**8*x3**2 - x1**2*x2**6*x3**4 - x1**2*x2**4*x3**6 + x1**2*x2**2*x3**8 + x2**6*x3**6</t>
@@ -838,7 +838,7 @@
     <t>IMO 2000 Q2</t>
   </si>
   <si>
-    <t>通分</t>
+    <t>common-denominator conversion</t>
   </si>
   <si>
     <t>1 - (x1**2 - 1 + x1**2*x3**2)*(x2**2 - 1 + x1**2*x2**2)*(x3**2 - 1 + x2**2*x3**2)</t>
@@ -862,10 +862,10 @@
     <t>problem 98</t>
   </si>
   <si>
-    <t>MOSP 2021（Mharchi Abdelmalek）</t>
-  </si>
-  <si>
-    <t>平方换元，积约束</t>
+    <t>MOSP 2021(Mharchi Abdelmalek)</t>
+  </si>
+  <si>
+    <t>square substitution,product constraint</t>
   </si>
   <si>
     <t>x1**8*x2**2*x3**2 + x1**6*x2**6 - 4*x1**6*x2**2*x3**4 + x1**6*x3**6 - 4*x1**4*x2**6*x3**2 + 6*x1**4*x2**4*x3**4 + x1**2*x2**8*x3**2 - 4*x1**2*x2**4*x3**6 + x1**2*x2**2*x3**8 + x2**6*x3**6</t>
@@ -919,13 +919,13 @@
     <t>Q 2</t>
   </si>
   <si>
-    <t>平方换元,积为1</t>
+    <t>square substitution,product equals 1</t>
   </si>
   <si>
     <t xml:space="preserve"> x1**8*x3**4 - x1**6*x2**2*x3**4 + x1**4*x2**8 - x1**4*x2**6*x3**2 - x1**2*x2**4*x3**6 + x2**4*x3**8</t>
   </si>
   <si>
-    <t>例6</t>
+    <t>Example 6</t>
   </si>
   <si>
     <t>x1**8*x3**4 - 2*x1**6*x2**4*x3**2 + x1**4*x2**8 + 3*x1**4*x2**4*x3**4 - 2*x1**4*x2**2*x3**6 - 2*x1**2*x2**6*x3**4 + x2**4*x3**8</t>
@@ -943,7 +943,7 @@
     <t>Russia 2000 (Popa Alexandru)</t>
   </si>
   <si>
-    <t>积为一 平方换元</t>
+    <t>product equals one square substitution</t>
   </si>
   <si>
     <t>x1**8*x3**4 - 2*x1**6*x2**4*x3**2 + x1**6*x2**2*x3**4 + x1**4*x2**8 + x1**4*x2**6*x3**2 - 2*x1**4*x2**2*x3**6 - 2*x1**2*x2**6*x3**4 + x1**2*x2**4*x3**6 + x2**4*x3**8</t>
@@ -1006,13 +1006,13 @@
     <t>2*x1**4 - 2*x1**3 - 2*x1 + 2</t>
   </si>
   <si>
-    <t>Motzkin 多项式</t>
+    <t>Motzkin Polynomial</t>
   </si>
   <si>
     <t>x1**4 * x2**2 + x1**2*x2**4 - 3 * x1**2 * x2**2 + 1</t>
   </si>
   <si>
-    <t>Choi-Lam 多项式</t>
+    <t>Choi-Lam Polynomial</t>
   </si>
   <si>
     <t>x1**4 * x2**2 + x2**4 + x1**2 - 3 * x1**2 * x2**2</t>
@@ -1025,7 +1025,7 @@
      + x1**2 * x2**4 + x1**4 + x1**4 * x2**2 + x1**6)</t>
   </si>
   <si>
-    <t>Leep-Starr 多项式</t>
+    <t>Leep-Starr Polynomial</t>
   </si>
   <si>
     <t xml:space="preserve"> (8 + 0.5 * x1**2 * x2**4 + x1**2 * x2**3 - 2 * x1**3 * x2**3 
@@ -1105,7 +1105,7 @@
     <t>x1**10*x2**10*x3**10 - x1**10*x2**10*x3**4 + 3*x1**10*x2**10 - x1**10*x2**4*x3**10 + x1**10*x2**4*x3**4 - 3*x1**10*x2**4 + 3*x1**10*x3**10 - 3*x1**10*x3**4 + 9*x1**10 - x1**6 - x1**4*x2**10*x3**10 + x1**4*x2**10*x3**4 - 3*x1**4*x2**10 + x1**4*x2**4*x3**10 - x1**4*x2**4*x3**4 + 3*x1**4*x2**4 - 3*x1**4*x2**2 - 3*x1**4*x3**10 + 3*x1**4*x3**4 - 3*x1**4*x3**2 - 9*x1**4 - 3*x1**2*x2**4 - 6*x1**2*x2**2*x3**2 - 3*x1**2*x3**4 + 3*x2**10*x3**10 - 3*x2**10*x3**4 + 9*x2**10 - x2**6 - 3*x2**4*x3**10 + 3*x2**4*x3**4 - 3*x2**4*x3**2 - 9*x2**4 - 3*x2**2*x3**4 + 9*x3**10 - x3**6 - 9*x3**4 + 27</t>
   </si>
   <si>
-    <t>有名例子，</t>
+    <t>famous example,</t>
   </si>
   <si>
     <t>example 1.1.1</t>
@@ -1114,7 +1114,7 @@
     <t>x1**2 - x1*x2 + x2**2 - x2*x3 + x3**2 - x1*x3</t>
   </si>
   <si>
-    <t>和 1 重复</t>
+    <t>same as 1 duplicate</t>
   </si>
   <si>
     <t>570 Nice And Hard Inequalities</t>
@@ -1126,13 +1126,13 @@
     <t xml:space="preserve"> (x1**2 + x2**2 + x3**2)**2 - 3*(x1**3*x2 + x2**3*x3 + x3**3*x1)</t>
   </si>
   <si>
-    <t xml:space="preserve"> 和9  21重复 </t>
+    <t xml:space="preserve"> same as9  21duplicate </t>
   </si>
   <si>
     <t>4f</t>
   </si>
   <si>
-    <t>和 9 17重复</t>
+    <t>same as 9 17duplicate</t>
   </si>
   <si>
     <t>Schur‘s Inequality r=1</t>
@@ -1141,13 +1141,13 @@
     <t xml:space="preserve"> x1**6 - x1**4*x2**2 - x1**4*x3**2 - x1**2*x2**4 + 3*x1**2*x2**2*x3**2 - x1**2*x3**4 + x2**6 - x2**4*x3**2 - x2**2*x3**4 + x3**6</t>
   </si>
   <si>
-    <t>和29</t>
+    <t>same as29</t>
   </si>
   <si>
     <t>I 89</t>
   </si>
   <si>
-    <t>？</t>
+    <t>?</t>
   </si>
   <si>
     <t>x1**6 - x1**4*x2**2 - x1**4*x3**2 - x1**2*x2**4 + 3*x1**2*x2**2*x3**2 - x1**2*x3**4 + x2**6 - x2**4*x3**2 - x2**2*x3**4 + x3**6</t>
@@ -1171,7 +1171,7 @@
     <t xml:space="preserve"> x1**6 - x1**4*x2**2 + x2**6 - x2**4*x3**2 + x3**6 - x1**2*x3**4</t>
   </si>
   <si>
-    <t>和23 重复</t>
+    <t>same as23 duplicate</t>
   </si>
   <si>
     <t>example 3.1.2</t>
@@ -1180,22 +1180,22 @@
     <t>x1**6 - x1**4*x2**2 + x2**6 - x2**4*x3**2 + x3**6 - x1**2*x3**4</t>
   </si>
   <si>
-    <t>和 23 47 重复</t>
-  </si>
-  <si>
-    <t>120个数学竞赛不等式</t>
-  </si>
-  <si>
-    <t>例91</t>
-  </si>
-  <si>
-    <t>和50</t>
+    <t>same as 23 47 duplicate</t>
+  </si>
+  <si>
+    <t>120 Math contest inequalities</t>
+  </si>
+  <si>
+    <t>Example 91</t>
+  </si>
+  <si>
+    <t>same as50</t>
   </si>
   <si>
     <t>problem 3.74</t>
   </si>
   <si>
-    <t>和 24 重复</t>
+    <t>same as 24 duplicate</t>
   </si>
   <si>
     <t>Exercise 1.60</t>
@@ -1207,31 +1207,31 @@
     <t xml:space="preserve">Example 1.1.4 </t>
   </si>
   <si>
-    <t>和70</t>
+    <t>same as70</t>
   </si>
   <si>
     <t>Exercise 3.1.2</t>
   </si>
   <si>
-    <t>和65</t>
+    <t>same as65</t>
   </si>
   <si>
     <t>Exercise 1.115</t>
   </si>
   <si>
-    <t>和85</t>
+    <t>same as85</t>
   </si>
   <si>
     <t>Q 18</t>
   </si>
   <si>
-    <t>和88</t>
-  </si>
-  <si>
-    <t>119个数学竞赛不等式</t>
-  </si>
-  <si>
-    <t>121个数学竞赛不等式</t>
+    <t>same as88</t>
+  </si>
+  <si>
+    <t>119 Math contest inequalities</t>
+  </si>
+  <si>
+    <t>121 Math contest inequalities</t>
   </si>
   <si>
     <t>Q 402</t>
@@ -1240,19 +1240,19 @@
     <t xml:space="preserve"> (x1**4 + x1**2*x2**2 + x2**4)*(x1**4 + x1**2*x3**2 + x3**4)*(x2**4 + x2**2*x3**2 + x3**4) - (x1**2*x2**2 + x1**2*x3**2 + x2**2*x3**2)**3</t>
   </si>
   <si>
-    <t>和111</t>
+    <t>same as111</t>
   </si>
   <si>
     <t>Q 1</t>
   </si>
   <si>
-    <t>和100</t>
-  </si>
-  <si>
-    <t>和102</t>
-  </si>
-  <si>
-    <t>和103</t>
+    <t>same as100</t>
+  </si>
+  <si>
+    <t>same as102</t>
+  </si>
+  <si>
+    <t>same as103</t>
   </si>
   <si>
     <t>568 Nice And Hard Inequalities</t>
@@ -1261,7 +1261,7 @@
     <t>569 Nice And Hard Inequalities</t>
   </si>
   <si>
-    <t>和124</t>
+    <t>same as124</t>
   </si>
   <si>
     <t>I 93</t>
@@ -1273,7 +1273,7 @@
     <t xml:space="preserve"> -(x1**2 + x2**2 + x3**2)**3 + (x1**10 - x1**4 + 3)*(x2**10 - x2**4 + 3)*(x3**10 - x3**4 + 3)</t>
   </si>
   <si>
-    <t>和138</t>
+    <t>same as138</t>
   </si>
   <si>
     <t>4 Problems 5</t>
@@ -1282,7 +1282,7 @@
     <t>(x1**10 - x1**4 + 3)*(x2**10 - x2**4 + 3)*(x3**10 - x3**4 + 3) - (x1**2 + x2**2 + x3**2)**3</t>
   </si>
   <si>
-    <t>可能算重复</t>
+    <t>may be duplicate</t>
   </si>
   <si>
     <t>ref29</t>
@@ -1327,7 +1327,7 @@
 )</t>
   </si>
   <si>
-    <t>lean statement太长报错</t>
+    <t>lean statementtoo long, raises an error</t>
   </si>
   <si>
     <t>Chapter 2 Problem 6</t>
@@ -1339,7 +1339,7 @@
     <t>-9*x1**2*x2**2 - 9*x1**2*x3**2 - 9*x2**2*x3**2 + (x1**4 + 2)*(x2**4 + 2)*(x3**4 + 2)</t>
   </si>
   <si>
-    <t>待补</t>
+    <t>to be completed</t>
   </si>
   <si>
     <t>Problem 3.85</t>
@@ -1348,7 +1348,7 @@
     <t>Q 404</t>
   </si>
   <si>
-    <t>重复</t>
+    <t>duplicate</t>
   </si>
   <si>
     <t>Q 35</t>
@@ -1363,7 +1363,7 @@
     <t xml:space="preserve"> (x1 + x2 - x3)**2 * (x2 + x3 - x1)**2 * (x3 + x1 - x2)**2 - (x1**2 + x2**2 - x3**2) * (x2**2 + x3**2 - x1**2) * (x3**2 + x1**2 - x2**2)</t>
   </si>
   <si>
-    <t>和54 重复</t>
+    <t>same as54 duplicate</t>
   </si>
   <si>
     <t>Q 37</t>
@@ -1375,10 +1375,10 @@
     <t>(x1**2 + x2**2 + x3**2)**2 - 3*(x1**3*x2 + x2**3*x3 + x3**3*x1)</t>
   </si>
   <si>
-    <t>和 87 重复</t>
-  </si>
-  <si>
-    <t>重复12</t>
+    <t>same as 87 duplicate</t>
+  </si>
+  <si>
+    <t>duplicate12</t>
   </si>
   <si>
     <t>Inequalities From Around the World 1995-2006 Solutions to ’Inequalities through problems’ by Hojoo Lee</t>
@@ -1390,10 +1390,10 @@
     <t>Inequalities From Around the World 1995-2007 Solutions to ’Inequalities through problems’ by Hojoo Lee</t>
   </si>
   <si>
-    <t>USA 2004  重复了？</t>
-  </si>
-  <si>
-    <t>重复83</t>
+    <t>USA 2004  duplicate?</t>
+  </si>
+  <si>
+    <t>duplicate83</t>
   </si>
   <si>
     <t>Inequalities From Around the World 1995-2008 Solutions to ’Inequalities through problems’ by Hojoo Lee</t>
@@ -1402,7 +1402,7 @@
     <t>3*(x1 + x2 + 1)**2 - 3*x1*x2 + 1</t>
   </si>
   <si>
-    <t>重复84</t>
+    <t>duplicate84</t>
   </si>
   <si>
     <t>Inequalities From Around the World 1995-2010 Solutions to ’Inequalities through problems’ by Hojoo Lee</t>
@@ -1414,25 +1414,25 @@
     <t xml:space="preserve"> 7*(x1 + x2)**4 + 7*(x2 + x3)**4 + 7*(x3 + x1)**4 - 4*(x1**4 + x2**4 + x3**4)</t>
   </si>
   <si>
-    <t>和85重复</t>
+    <t>same as85duplicate</t>
   </si>
   <si>
     <t>Inequalities From Around the World 1995-2012 Solutions to ’Inequalities through problems’ by Hojoo Lee</t>
   </si>
   <si>
-    <t>和86 54 重复</t>
+    <t>same as86 54 duplicate</t>
   </si>
   <si>
     <t>Inequalities From Around the World 1995-2015 Solutions to ’Inequalities through problems’ by Hojoo Lee</t>
   </si>
   <si>
-    <t>和87重复</t>
+    <t>same as87duplicate</t>
   </si>
   <si>
     <t xml:space="preserve"> (x1**2 + x2**2)*(x1**2 + x3**2)*(x2**2 + x3**2) - 8*x1**2*x2**2*x3**2</t>
   </si>
   <si>
-    <t>和18重复</t>
+    <t>same as18duplicate</t>
   </si>
   <si>
     <t>example 1.1.4</t>
@@ -1441,28 +1441,28 @@
     <t>x1**6 - 2*x1**4*x2**2 + x1**4*x3**2 + x1**2*x2**4 - 2*x1**2*x3**4 + x2**6 - 2*x2**4*x3**2 + x2**2*x3**4 + x3**6</t>
   </si>
   <si>
-    <t>和19重复</t>
+    <t>same as19duplicate</t>
   </si>
   <si>
     <t>3*(x1**2 + x2**2 + x3**2) - (x1 + x2 + x3)**2</t>
   </si>
   <si>
-    <t>和4重复</t>
+    <t>same as4duplicate</t>
   </si>
   <si>
     <t>example 3.1.1</t>
   </si>
   <si>
-    <t>和100重复</t>
-  </si>
-  <si>
-    <t>和20重复</t>
+    <t>same as100duplicate</t>
+  </si>
+  <si>
+    <t>same as20duplicate</t>
   </si>
   <si>
     <t>x1**2*x2**2*x3**2 + x1**2 - 2*x1*x2 + x2**2 - 2*x2*x3 + x3**2 - 2*x1*x3 + 2</t>
   </si>
   <si>
-    <t>和5重复</t>
+    <t>same as5duplicate</t>
   </si>
   <si>
     <t>ELMO shortlist 2012</t>
@@ -1471,7 +1471,7 @@
     <t xml:space="preserve"> (x1**4 + x2**4 + x3**4)**2012 + 2*(x1**2*x2**2 + x2**2*x3**2 + x3**2*x1**2)**2012 - ((x1**4 + 2*x2**2*x3**2)**2012 +  (x2**4 + 2*x3**2*x1**2)**2012 +  (x3**4 + 2*x1**2*x2**2)**2012)</t>
   </si>
   <si>
-    <t>次数太高，删掉</t>
+    <t>Degreetoo high, removed</t>
   </si>
   <si>
     <t>problem 25</t>
@@ -1579,7 +1579,7 @@
     <t>3*(x1**6 + x2**6 + x3**6 + x1**2*x2**2*x3**2) - 4*(x1**4*x2**2 + x2**4*x3**2 + x3**4*x1**2)</t>
   </si>
   <si>
-    <t>和68 60 57重复</t>
+    <t>same as68 60 57duplicate</t>
   </si>
   <si>
     <t xml:space="preserve">A Brief Introduction to Olympiad Inequalities </t>
@@ -1591,16 +1591,16 @@
     <t>exercise 3.1.2</t>
   </si>
   <si>
-    <t>待确定是否重复</t>
-  </si>
-  <si>
-    <t>flyspeck带约束，不算</t>
-  </si>
-  <si>
-    <t>有名例子可再添加</t>
-  </si>
-  <si>
-    <t>求 Bernstein基的时候尝试用的带约束例子</t>
+    <t>pending duplicate check</t>
+  </si>
+  <si>
+    <t>flyspeckhas constraints, not counted</t>
+  </si>
+  <si>
+    <t>famous example, can be added later</t>
+  </si>
+  <si>
+    <t>constrained example tried when computing the Bernstein basis</t>
   </si>
   <si>
     <t>CVPR</t>
@@ -1618,7 +1618,7 @@
     <t>[-1.5,2],x1*x2**2+x1*x3**2-1.1*x1+10.35</t>
   </si>
   <si>
-    <t>有约束/难度？</t>
+    <t>constraints/difficulty?</t>
   </si>
   <si>
     <t>[-2,2],x1*x2**2+x1*x3**2+x1*x4**2-1.1*x1+21.8</t>
@@ -1657,11 +1657,11 @@
     <t>[-1, 1],x1**2 + 2*x2**2 + 2*x3**2 + 2*x4**2 + 2*x5**2 + 2*x6**2 + 2*x7**2 - x1 + 0.25001</t>
   </si>
   <si>
-    <t># 👇有约束 x1:[−1,0], x2:[−0.1,0.9], x3:[−0.1,0.5], x4:[−1, −0.1], x5:[−0.1, −0.05], x6:[−0.1, −0.03]
+    <t># constrained x1:[−1,0], x2:[−0.1,0.9], x3:[−0.1,0.5], x4:[−1, −0.1], x5:[−0.1, −0.05], x6:[−0.1, −0.03]
     x6*x2**2 + x5*x3**2 - x1*x4**2 + x4**3 + x4**2 - (1/3)*x1 + (4/3)*x4 + 1.44</t>
   </si>
   <si>
-    <t># 👇有约束 x1:[−0.1, 0.4],x2:[0.4, 1],x3:[−0.7, −0.4],x4:[−0.7, 0.4],x5:[0.1, 0.2],x6:[−0.1, 0.2],x7:[−0.3, 1.1],x8:[−1.1, −0.3], 
+    <t># constrained x1:[−0.1, 0.4],x2:[0.4, 1],x3:[−0.7, −0.4],x4:[−0.7, 0.4],x5:[0.1, 0.2],x6:[−0.1, 0.2],x7:[−0.3, 1.1],x8:[−1.1, −0.3], 
     -1*(x1*x6**3) + 3*x1*x6*x7**2 - x3*x7**3 + 3*x3*x7*x6**2 - x2*x5**3 +3*x2*x5*x8**2 - x4*x8**3 + 3*x4*x8*x5**2 - 0.9563453 + 1.7435</t>
   </si>
 </sst>
@@ -1673,7 +1673,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1681,21 +1681,21 @@
       <b/>
       <sz val="9.75"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9.75"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9.75"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1703,7 +1703,7 @@
       <b/>
       <sz val="10.5"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1711,7 +1711,7 @@
       <b/>
       <sz val="9.75"/>
       <color rgb="FF245BDB"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1719,21 +1719,21 @@
       <b/>
       <sz val="9.75"/>
       <color rgb="FFF54A45"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9.75"/>
       <color rgb="FFF54A45"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9.75"/>
       <color rgb="FF1F2329"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1742,13 +1742,13 @@
       <strike/>
       <sz val="9.75"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2338,7 +2338,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2409,12 +2409,12 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="左若冰" id="{B8C2CF68-4171-4CBF-9447-267638078D0D}" userId="S::::71061df2-afea-4f61-8d53-773a5329c1e4" providerId="AD"/>
+  <person displayName="Ruobing Zuo" id="{B8C2CF68-4171-4CBF-9447-267638078D0D}" userId="S::::71061df2-afea-4f61-8d53-773a5329c1e4" providerId="AD"/>
 </personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2459,10 +2459,10 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="Yu Gothic Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hans" typeface="DengXian Light"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -2511,10 +2511,10 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="Yu Gothic"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hans" typeface="DengXian"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -2711,13 +2711,13 @@
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="H31" dT="2025-07-19T10:58:07.00" personId="{B8C2CF68-4171-4CBF-9447-267638078D0D}" id="{13F3242D-3C96-4BAF-8E56-D37E0E60D55A}">
-    <text>本身部分展开就是SOS？</text>
+    <text>Is the partial expansion itself SOS?</text>
   </threadedComment>
   <threadedComment ref="C41" dT="2025-07-20T13:30:39.00" personId="{B8C2CF68-4171-4CBF-9447-267638078D0D}" id="{6A84E58D-0B2C-4B23-B644-E10E2FB2A9FB}">
-    <text>由于r=1时，二次舒尔不等式经过平方换元后和Robinson不等式重复了，所以这里换成四次舒尔不等式再平方换元</text>
+    <text>When r=1, the quadratic Schur inequality duplicates the Robinson inequality after square substitution, so this is changed to the quartic Schur inequality followed by square substitution</text>
   </threadedComment>
   <threadedComment ref="H45" dT="2025-07-19T10:49:56.00" personId="{B8C2CF68-4171-4CBF-9447-267638078D0D}" id="{B1015C5D-D2D7-4328-8F98-E690265FCF2E}">
-    <text>为了方便找SOS，可能还是展开比较好?</text>
+    <text>For easier SOS search, expansion may still be better?</text>
   </threadedComment>
 </ThreadedComments>
 </file>
